--- a/cour/cour formation/RCP101/Exercice SOLVEUR.xlsx
+++ b/cour/cour formation/RCP101/Exercice SOLVEUR.xlsx
@@ -8,130 +8,176 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\cour\cour formation\RCP101\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48CD1E88-9B89-438E-8EF5-708EFD0A7F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E774E7-D17C-4F0B-A684-247971CA1F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{90B57167-D7BE-4612-82E1-46C9B2A4F86F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{90B57167-D7BE-4612-82E1-46C9B2A4F86F}"/>
   </bookViews>
   <sheets>
     <sheet name="Exo diapo 107" sheetId="1" r:id="rId1"/>
     <sheet name="Td PL 01" sheetId="2" r:id="rId2"/>
     <sheet name="Td PL 02" sheetId="3" r:id="rId3"/>
+    <sheet name="Entrainement Sportif" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="3" hidden="1">'Entrainement Sportif'!$E$5:$F$5</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'Exo diapo 107'!$D$6:$E$6</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'Td PL 01'!$D$5:$F$5</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'Td PL 02'!$E$7:$H$7</definedName>
+    <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs0" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$17</definedName>
+    <definedName name="solver_lhs1" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$15</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Exo diapo 107'!$F$10</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'Td PL 01'!$D$5</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'Td PL 02'!$I$10</definedName>
+    <definedName name="solver_lhs2" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$16</definedName>
     <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Exo diapo 107'!$F$11</definedName>
     <definedName name="solver_lhs2" localSheetId="1" hidden="1">'Td PL 01'!$D$8:$F$8</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'Td PL 02'!$I$11</definedName>
+    <definedName name="solver_lhs3" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$17</definedName>
     <definedName name="solver_lhs3" localSheetId="0" hidden="1">'Exo diapo 107'!$F$9</definedName>
     <definedName name="solver_lhs3" localSheetId="1" hidden="1">'Td PL 01'!$D$9:$F$9</definedName>
     <definedName name="solver_lhs3" localSheetId="2" hidden="1">'Td PL 02'!$I$12</definedName>
+    <definedName name="solver_lhs4" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$18</definedName>
     <definedName name="solver_lhs4" localSheetId="1" hidden="1">'Td PL 01'!$E$5</definedName>
     <definedName name="solver_lhs4" localSheetId="2" hidden="1">'Td PL 02'!$I$13</definedName>
+    <definedName name="solver_lhs5" localSheetId="3" hidden="1">'Entrainement Sportif'!$G$19</definedName>
     <definedName name="solver_lhs5" localSheetId="1" hidden="1">'Td PL 01'!$F$5</definedName>
+    <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">5</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">5</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">4</definedName>
+    <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">'Entrainement Sportif'!$E$11</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'Exo diapo 107'!$H$6</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'Td PL 01'!$H$5</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'Td PL 02'!$K$6</definedName>
+    <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel0" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel3" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel3" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rel3" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel4" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_rel4" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_rel5" localSheetId="1" hidden="1">3</definedName>
+    <definedName name="solver_rhs0" localSheetId="3" hidden="1">'Entrainement Sportif'!$I$17</definedName>
+    <definedName name="solver_rhs1" localSheetId="3" hidden="1">'Entrainement Sportif'!$I$15</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'Exo diapo 107'!$G$10</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'Td PL 01'!$J$10</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">'Td PL 02'!$J$10</definedName>
+    <definedName name="solver_rhs2" localSheetId="3" hidden="1">'Entrainement Sportif'!$I$16</definedName>
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">'Exo diapo 107'!$G$11</definedName>
     <definedName name="solver_rhs2" localSheetId="1" hidden="1">'Td PL 01'!$I$8</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'Td PL 02'!$J$11</definedName>
+    <definedName name="solver_rhs3" localSheetId="3" hidden="1">'Entrainement Sportif'!$H$17</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">'Exo diapo 107'!$G$9</definedName>
     <definedName name="solver_rhs3" localSheetId="1" hidden="1">'Td PL 01'!$I$9</definedName>
     <definedName name="solver_rhs3" localSheetId="2" hidden="1">'Td PL 02'!$J$12</definedName>
+    <definedName name="solver_rhs4" localSheetId="3" hidden="1">'Entrainement Sportif'!$H$18</definedName>
     <definedName name="solver_rhs4" localSheetId="1" hidden="1">'Td PL 01'!$E$11</definedName>
     <definedName name="solver_rhs4" localSheetId="2" hidden="1">'Td PL 02'!$J$13</definedName>
+    <definedName name="solver_rhs5" localSheetId="3" hidden="1">'Entrainement Sportif'!$H$19</definedName>
     <definedName name="solver_rhs5" localSheetId="1" hidden="1">'Td PL 01'!$F$11</definedName>
+    <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
@@ -157,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="48">
   <si>
     <t>Nb Chausson</t>
   </si>
@@ -247,13 +293,67 @@
   </si>
   <si>
     <t>Nb M4 HD</t>
+  </si>
+  <si>
+    <t>Contraintes</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Fonction Objectif</t>
+  </si>
+  <si>
+    <t>Variables de décision</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>X2&gt;= 1/3 X1</t>
+  </si>
+  <si>
+    <t>x1 + X2 &gt;= 20</t>
+  </si>
+  <si>
+    <t>X1 &gt;=10</t>
+  </si>
+  <si>
+    <t>X2&lt;=15</t>
+  </si>
+  <si>
+    <t>X1 &lt;= 25</t>
+  </si>
+  <si>
+    <t>Cout Minimal</t>
+  </si>
+  <si>
+    <t>F : 10x1 + 12x2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>x2 : Nbre d'heures sur Route</t>
+  </si>
+  <si>
+    <t>x1 : Nbre heures en Salle</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>MODELISATION</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,8 +361,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,8 +402,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -296,11 +435,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -314,9 +468,22 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -896,7 +1063,6 @@
         <f>F5*2</f>
         <v>36</v>
       </c>
-      <c r="H10" s="5"/>
       <c r="J10" s="1">
         <f>E5+(2*F5)</f>
         <v>71</v>
@@ -1094,4 +1260,204 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD8865B-EE7C-422F-92C2-325AB47AF4A3}">
+  <dimension ref="B2:K20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.08984375" customWidth="1"/>
+    <col min="4" max="4" width="2.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="12">
+        <v>15</v>
+      </c>
+      <c r="F5" s="11">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="9">
+        <f>(E5*E10)+(F5*F10)</f>
+        <v>210</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="E14" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="6">
+        <f>$E$5</f>
+        <v>15</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="6">
+        <f>$F$5</f>
+        <v>5</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="6">
+        <f>$E$5</f>
+        <v>15</v>
+      </c>
+      <c r="H17" s="5">
+        <v>10</v>
+      </c>
+      <c r="I17" s="5"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="6">
+        <f>$E$5+$F$5</f>
+        <v>20</v>
+      </c>
+      <c r="H18" s="5">
+        <v>20</v>
+      </c>
+      <c r="I18" s="5"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="6">
+        <f>F5</f>
+        <v>5</v>
+      </c>
+      <c r="H19" s="5">
+        <f>1/3*$E$5</f>
+        <v>5</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>